--- a/docs/data/Format Template.xlsx
+++ b/docs/data/Format Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\sampah\item\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\Project\RUST\Tridjaya Manado\docs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789A6FA2-A1A9-4853-A60F-F1293AD210B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB375DE-08F0-4B8D-B0AE-80537ED832B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{0986F36E-3325-4F5B-8A54-5856074FD1D1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>No</t>
   </si>
@@ -65,70 +65,13 @@
     <t>anca</t>
   </si>
   <si>
-    <t>+62 812-4445-9180</t>
-  </si>
-  <si>
-    <t>amel</t>
-  </si>
-  <si>
-    <t>+62 838-9529-5471</t>
-  </si>
-  <si>
-    <t>risna</t>
-  </si>
-  <si>
-    <t>+62 853-4040-7005</t>
-  </si>
-  <si>
-    <t>kak</t>
-  </si>
-  <si>
-    <t>+62 823-5340-6614</t>
-  </si>
-  <si>
-    <t>fey</t>
-  </si>
-  <si>
-    <t>+62 821-8731-8485</t>
-  </si>
-  <si>
-    <t>dayo</t>
-  </si>
-  <si>
-    <t>+62 877-6631-1432</t>
-  </si>
-  <si>
-    <t>eyo</t>
-  </si>
-  <si>
-    <t>+62 856-5708-5482</t>
-  </si>
-  <si>
-    <t>yara</t>
-  </si>
-  <si>
-    <t>+62 812-4117-966</t>
-  </si>
-  <si>
-    <t>Magdalena</t>
-  </si>
-  <si>
-    <t>+62 882-0201-29842</t>
-  </si>
-  <si>
-    <t>Mhyra</t>
-  </si>
-  <si>
-    <t>+62 821-4810-3387</t>
-  </si>
-  <si>
-    <t>asky</t>
-  </si>
-  <si>
-    <t>+62 822-9600-3031</t>
-  </si>
-  <si>
-    <t>etan</t>
+    <t>+62 823-3923-5048</t>
+  </si>
+  <si>
+    <t>+62 882-0212-23128</t>
+  </si>
+  <si>
+    <t>yane 2</t>
   </si>
 </sst>
 </file>
@@ -549,10 +492,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -560,10 +503,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1">
-        <v>82339235048</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,121 +514,61 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/data/Format Template.xlsx
+++ b/docs/data/Format Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\Project\RUST\Tridjaya Manado\docs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB375DE-08F0-4B8D-B0AE-80537ED832B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9F4CD9-4D2B-4EFE-9DC5-6B256ECC397D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{0986F36E-3325-4F5B-8A54-5856074FD1D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0986F36E-3325-4F5B-8A54-5856074FD1D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="235">
   <si>
     <t>No</t>
   </si>
@@ -50,40 +50,720 @@
     <t>Wa</t>
   </si>
   <si>
-    <t>+62 896-5377-1753</t>
-  </si>
-  <si>
-    <t>yane</t>
-  </si>
-  <si>
-    <t>+62 852-5615-5638</t>
-  </si>
-  <si>
-    <t>abdon</t>
-  </si>
-  <si>
-    <t>anca</t>
-  </si>
-  <si>
-    <t>+62 823-3923-5048</t>
-  </si>
-  <si>
-    <t>+62 882-0212-23128</t>
-  </si>
-  <si>
-    <t>yane 2</t>
+    <t>+62 895-8048-77256</t>
+  </si>
+  <si>
+    <t>+62 853-9942-7249</t>
+  </si>
+  <si>
+    <t>+62 813-5674-0563</t>
+  </si>
+  <si>
+    <t>+62 878-3283-3122</t>
+  </si>
+  <si>
+    <t>+62 814-4581-8417</t>
+  </si>
+  <si>
+    <t>+62 822-9272-7226</t>
+  </si>
+  <si>
+    <t>+62 821-9503-3726</t>
+  </si>
+  <si>
+    <t>+62 819-5375-3552</t>
+  </si>
+  <si>
+    <t>+62 821-8908-8497</t>
+  </si>
+  <si>
+    <t>+62 812-1414-5647</t>
+  </si>
+  <si>
+    <t>+62 815-2722-1267</t>
+  </si>
+  <si>
+    <t>+62 821-9109-6270</t>
+  </si>
+  <si>
+    <t>+62 822-1173-0056</t>
+  </si>
+  <si>
+    <t>+62 853-4025-3656</t>
+  </si>
+  <si>
+    <t>+62 811-4396-848</t>
+  </si>
+  <si>
+    <t>+62 821-9245-2778</t>
+  </si>
+  <si>
+    <t>+62 852-8250-0419</t>
+  </si>
+  <si>
+    <t>+62 813-4014-8444</t>
+  </si>
+  <si>
+    <t>+62 852-4232-6575</t>
+  </si>
+  <si>
+    <t>+62 811-4330-689</t>
+  </si>
+  <si>
+    <t>+62 821-9093-2553</t>
+  </si>
+  <si>
+    <t>+62 896-7641-2683</t>
+  </si>
+  <si>
+    <t>+62 821-9143-1860</t>
+  </si>
+  <si>
+    <t>+62 831-8952-1057</t>
+  </si>
+  <si>
+    <t>+62 812-4435-5055</t>
+  </si>
+  <si>
+    <t>+62 853-1390-6976</t>
+  </si>
+  <si>
+    <t>+62 851-6681-5867</t>
+  </si>
+  <si>
+    <t>+62 812-3324-6345</t>
+  </si>
+  <si>
+    <t>+62 821-8737-755</t>
+  </si>
+  <si>
+    <t>+62 815-2587-2271</t>
+  </si>
+  <si>
+    <t>+62 812-4383-5697</t>
+  </si>
+  <si>
+    <t>+62 852-9850-5154</t>
+  </si>
+  <si>
+    <t>+62 822-9153-8432</t>
+  </si>
+  <si>
+    <t>+62 857-2822-8106</t>
+  </si>
+  <si>
+    <t>+62 822-3174-9561</t>
+  </si>
+  <si>
+    <t>+62 823-9343-2725</t>
+  </si>
+  <si>
+    <t>+62 857-5696-8656</t>
+  </si>
+  <si>
+    <t>+62 896-1243-2623</t>
+  </si>
+  <si>
+    <t>+62 821-9141-3038</t>
+  </si>
+  <si>
+    <t>+62 813-5488-6253</t>
+  </si>
+  <si>
+    <t>+62 812-4382-6373</t>
+  </si>
+  <si>
+    <t>+62 822-9151-5197</t>
+  </si>
+  <si>
+    <t>+62 821-9277-2545</t>
+  </si>
+  <si>
+    <t>+62 821-8707-9977</t>
+  </si>
+  <si>
+    <t>+62 823-9915-1754</t>
+  </si>
+  <si>
+    <t>+62 852-5621-5777</t>
+  </si>
+  <si>
+    <t>+62 831-9883-2426</t>
+  </si>
+  <si>
+    <t>+62 853-9955-8534</t>
+  </si>
+  <si>
+    <t>+62 821-8822-4911</t>
+  </si>
+  <si>
+    <t>+62 858-8888-6532</t>
+  </si>
+  <si>
+    <t>+62 812-4352-9011</t>
+  </si>
+  <si>
+    <t>+62 857-1249-2069</t>
+  </si>
+  <si>
+    <t>+62 896-9498-4044</t>
+  </si>
+  <si>
+    <t>+62 822-4919-4955</t>
+  </si>
+  <si>
+    <t>+62 822-9248-8983</t>
+  </si>
+  <si>
+    <t>+62 813-4070-4000</t>
+  </si>
+  <si>
+    <t>+62 851-6192-5226</t>
+  </si>
+  <si>
+    <t>+62 823-4797-6654</t>
+  </si>
+  <si>
+    <t>+62 852-9812-2994</t>
+  </si>
+  <si>
+    <t>+62 812-4230-4815</t>
+  </si>
+  <si>
+    <t>+62 852-4095-6445</t>
+  </si>
+  <si>
+    <t>+62 852-4066-1072</t>
+  </si>
+  <si>
+    <t>+62 853-9637-9585</t>
+  </si>
+  <si>
+    <t>+62 819-9358-3145</t>
+  </si>
+  <si>
+    <t>+62 852-4002-0714</t>
+  </si>
+  <si>
+    <t>+62 853-4377-8900</t>
+  </si>
+  <si>
+    <t>+62 852-4171-8730</t>
+  </si>
+  <si>
+    <t>+62 895-2549-0600</t>
+  </si>
+  <si>
+    <t>+62 896-0953-9070</t>
+  </si>
+  <si>
+    <t>+62 895-2889-1498</t>
+  </si>
+  <si>
+    <t>+62 857-5434-7574</t>
+  </si>
+  <si>
+    <t>+62 851-6942-9311</t>
+  </si>
+  <si>
+    <t>+62 887-0534-9786</t>
+  </si>
+  <si>
+    <t>+62 852-1378-8272</t>
+  </si>
+  <si>
+    <t>+62 821-9673-5213</t>
+  </si>
+  <si>
+    <t>+62 821-9579-0490</t>
+  </si>
+  <si>
+    <t>+62 821-5265-5005</t>
+  </si>
+  <si>
+    <t>+62 821-8905-3355</t>
+  </si>
+  <si>
+    <t>+62 813-5614-0388</t>
+  </si>
+  <si>
+    <t>+62 856-5615-8289</t>
+  </si>
+  <si>
+    <t>+62 821-8767-8325</t>
+  </si>
+  <si>
+    <t>+62 821-9485-4752</t>
+  </si>
+  <si>
+    <t>+62 852-9894-2102</t>
+  </si>
+  <si>
+    <t>+62 853-9957-4967</t>
+  </si>
+  <si>
+    <t>+62 853-9822-5899</t>
+  </si>
+  <si>
+    <t>+62 812-4346-2782</t>
+  </si>
+  <si>
+    <t>+62 896-3038-9032</t>
+  </si>
+  <si>
+    <t>+62 896-2443-2434</t>
+  </si>
+  <si>
+    <t>+62 895-0423-7326</t>
+  </si>
+  <si>
+    <t>+62 813-4005-3806</t>
+  </si>
+  <si>
+    <t>+62 853-9693-4880</t>
+  </si>
+  <si>
+    <t>+62 821-9678-6226</t>
+  </si>
+  <si>
+    <t>+62 815-2776-0892</t>
+  </si>
+  <si>
+    <t>+62 895-3257-85871</t>
+  </si>
+  <si>
+    <t>+62 895-3707-02120</t>
+  </si>
+  <si>
+    <t>+62 853-9692-2209</t>
+  </si>
+  <si>
+    <t>+62 896-3554-7397</t>
+  </si>
+  <si>
+    <t>+62 813-5607-8688</t>
+  </si>
+  <si>
+    <t>+62 821-1489-5635</t>
+  </si>
+  <si>
+    <t>+62 853-4079-2005</t>
+  </si>
+  <si>
+    <t>+62 812-4005-8883</t>
+  </si>
+  <si>
+    <t>+62 852-4050-0049</t>
+  </si>
+  <si>
+    <t>+62 813-4783-5154</t>
+  </si>
+  <si>
+    <t>+65 8393 0975</t>
+  </si>
+  <si>
+    <t>+62 813-5699-6026</t>
+  </si>
+  <si>
+    <t>+62 812-8196-5989</t>
+  </si>
+  <si>
+    <t>+62 823-2283-1348</t>
+  </si>
+  <si>
+    <t>+62 896-9812-0771</t>
+  </si>
+  <si>
+    <t>+62 852-4030-7163</t>
+  </si>
+  <si>
+    <t>+62 819-3533-6985</t>
+  </si>
+  <si>
+    <t>+62 882-0208-45008</t>
+  </si>
+  <si>
+    <t>+62 831-2658-1301</t>
+  </si>
+  <si>
+    <t>+62 822-1189-0811</t>
+  </si>
+  <si>
+    <t>+62 851-1713-1229</t>
+  </si>
+  <si>
+    <t>+62 877-6631-1072</t>
+  </si>
+  <si>
+    <t>+62 821-5253-4778</t>
+  </si>
+  <si>
+    <t>RUSYDI</t>
+  </si>
+  <si>
+    <t>NETTY</t>
+  </si>
+  <si>
+    <t>CORRY</t>
+  </si>
+  <si>
+    <t>JUNAIDY</t>
+  </si>
+  <si>
+    <t>KSM</t>
+  </si>
+  <si>
+    <t>INDRI</t>
+  </si>
+  <si>
+    <t>NABILA</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>ANATJE</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>MONN</t>
+  </si>
+  <si>
+    <t>ELDA</t>
+  </si>
+  <si>
+    <t>ANDRE</t>
+  </si>
+  <si>
+    <t>ONAL</t>
+  </si>
+  <si>
+    <t>REGINA</t>
+  </si>
+  <si>
+    <t>MARK</t>
+  </si>
+  <si>
+    <t>SRI</t>
+  </si>
+  <si>
+    <t>HALIM</t>
+  </si>
+  <si>
+    <t>JUDIN</t>
+  </si>
+  <si>
+    <t>BAHAIS</t>
+  </si>
+  <si>
+    <t>HM</t>
+  </si>
+  <si>
+    <t>JOULA</t>
+  </si>
+  <si>
+    <t>MERRY</t>
+  </si>
+  <si>
+    <t>MELONDA</t>
+  </si>
+  <si>
+    <t>REKI</t>
+  </si>
+  <si>
+    <t>STEVEN</t>
+  </si>
+  <si>
+    <t>SENITSHA</t>
+  </si>
+  <si>
+    <t>NUR</t>
+  </si>
+  <si>
+    <t>CINTA</t>
+  </si>
+  <si>
+    <t>BLESS</t>
+  </si>
+  <si>
+    <t>UCARU</t>
+  </si>
+  <si>
+    <t>HUSANA</t>
+  </si>
+  <si>
+    <t>JACKY</t>
+  </si>
+  <si>
+    <t>TAMI</t>
+  </si>
+  <si>
+    <t>MEYU</t>
+  </si>
+  <si>
+    <t>MUCADRI</t>
+  </si>
+  <si>
+    <t>MILA</t>
+  </si>
+  <si>
+    <t>VIRGIN</t>
+  </si>
+  <si>
+    <t>BELGI</t>
+  </si>
+  <si>
+    <t>ALFIAN</t>
+  </si>
+  <si>
+    <t>DIAN</t>
+  </si>
+  <si>
+    <t>HENNI</t>
+  </si>
+  <si>
+    <t>DEBORA</t>
+  </si>
+  <si>
+    <t>SENDI</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>LBH</t>
+  </si>
+  <si>
+    <t>NIHIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALFI </t>
+  </si>
+  <si>
+    <t>RIAN</t>
+  </si>
+  <si>
+    <t>SKIVO</t>
+  </si>
+  <si>
+    <t>LOV</t>
+  </si>
+  <si>
+    <t>HAZA</t>
+  </si>
+  <si>
+    <t>MEITI</t>
+  </si>
+  <si>
+    <t>ILDY</t>
+  </si>
+  <si>
+    <t>DENNY</t>
+  </si>
+  <si>
+    <t>HARIANTO</t>
+  </si>
+  <si>
+    <t>CITRA</t>
+  </si>
+  <si>
+    <t>YUSUF</t>
+  </si>
+  <si>
+    <t>VEIBY</t>
+  </si>
+  <si>
+    <t>NOVIAN</t>
+  </si>
+  <si>
+    <t>RUDDY</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>BERTI</t>
+  </si>
+  <si>
+    <t>TIKA</t>
+  </si>
+  <si>
+    <t>DOHA</t>
+  </si>
+  <si>
+    <t>ANGELIA</t>
+  </si>
+  <si>
+    <t>WULAN</t>
+  </si>
+  <si>
+    <t>ALVI</t>
+  </si>
+  <si>
+    <t>KOL</t>
+  </si>
+  <si>
+    <t>NITA</t>
+  </si>
+  <si>
+    <t>RITAWATI</t>
+  </si>
+  <si>
+    <t>SONNY</t>
+  </si>
+  <si>
+    <t>YUNUS</t>
+  </si>
+  <si>
+    <t>RINI</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>SJELVIE</t>
+  </si>
+  <si>
+    <t>ANSELA</t>
+  </si>
+  <si>
+    <t>JUANDI</t>
+  </si>
+  <si>
+    <t>ZHARA</t>
+  </si>
+  <si>
+    <t>RAHMAWATI</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>FERDI</t>
+  </si>
+  <si>
+    <t>ADE KAI</t>
+  </si>
+  <si>
+    <t>SYENNY</t>
+  </si>
+  <si>
+    <t>TISEN</t>
+  </si>
+  <si>
+    <t>JEANE</t>
+  </si>
+  <si>
+    <t>DEWINTA</t>
+  </si>
+  <si>
+    <t>APRILIA</t>
+  </si>
+  <si>
+    <t>BILLY</t>
+  </si>
+  <si>
+    <t>OPS</t>
+  </si>
+  <si>
+    <t>NORMA</t>
+  </si>
+  <si>
+    <t>ANSFLY</t>
+  </si>
+  <si>
+    <t>REVAN</t>
+  </si>
+  <si>
+    <t>KARIN</t>
+  </si>
+  <si>
+    <t>HANNA</t>
+  </si>
+  <si>
+    <t>FIKRI</t>
+  </si>
+  <si>
+    <t>FALCO</t>
+  </si>
+  <si>
+    <t>FRANSISKUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIA </t>
+  </si>
+  <si>
+    <t>DIMAS</t>
+  </si>
+  <si>
+    <t>AHLAN</t>
+  </si>
+  <si>
+    <t>MATTHEW</t>
+  </si>
+  <si>
+    <t>EBHY</t>
+  </si>
+  <si>
+    <t>MAUREN</t>
+  </si>
+  <si>
+    <t>AYU</t>
+  </si>
+  <si>
+    <t>NHI</t>
+  </si>
+  <si>
+    <t>CHARLIO</t>
+  </si>
+  <si>
+    <t>NP</t>
+  </si>
+  <si>
+    <t>CYNTIA</t>
+  </si>
+  <si>
+    <t>GISYA</t>
+  </si>
+  <si>
+    <t>PUTRIA</t>
+  </si>
+  <si>
+    <t>AJW</t>
+  </si>
+  <si>
+    <t>FELDY</t>
+  </si>
+  <si>
+    <t>RIA</t>
+  </si>
+  <si>
+    <t>CORRI</t>
+  </si>
+  <si>
+    <t>FREED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -119,15 +799,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{EBC7BFC6-7BD8-4889-95A5-9968DCCD5317}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -459,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB274E24-97D7-4E48-B931-5D9D29701040}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
@@ -480,10 +1169,10 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -491,84 +1180,1409 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
+      <c r="B3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
+      <c r="B4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
